--- a/data/samples/samples/苏48-12-66X_D06_2026-03-06.xlsx
+++ b/data/samples/samples/苏48-12-66X_D06_2026-03-06.xlsx
@@ -1053,35 +1053,35 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>08:00 08:45 接单根，耗时 12 分钟。</t>
+          <t>08:45 08:45 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>11:00 11:45 循环调整泥浆性能，密度提至 1.18 g/cm3，漏斗粘度 42 s。</t>
+          <t>11:45 11:45 循环调整泥浆性能，密度提至 1.18 g/cm3，漏斗粘度 42 s。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>13:00 13:30 接单根，耗时 12 分钟。</t>
+          <t>13:30 13:30 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>16:00 16:45 地质录井汇报：岩性为灰色细砂岩，荧光显示 1 级。</t>
+          <t>16:45 16:45 地质录井汇报：岩性为灰色细砂岩，荧光显示 1 级。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>18:00 18:15 循环调整泥浆性能，密度提至 1.14 g/cm3，漏斗粘度 51 s。</t>
+          <t>18:15 18:15 循环调整泥浆性能，密度提至 1.14 g/cm3，漏斗粘度 51 s。</t>
         </is>
       </c>
     </row>
